--- a/demos/rct_experiment/rct_experiment_prompt_template.xlsx
+++ b/demos/rct_experiment/rct_experiment_prompt_template.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/rct_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57354155-BB78-1E49-9C43-22A4A64CA567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DA868B-B4AB-C540-B89E-784649CCF537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1840" yWindow="-21100" windowWidth="19420" windowHeight="20140" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="3760" windowWidth="34560" windowHeight="20140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="experimental_setting" sheetId="1" r:id="rId1"/>
-    <sheet name="treatments" sheetId="2" r:id="rId2"/>
-    <sheet name="roles" sheetId="3" r:id="rId3"/>
-    <sheet name="interview_prompts" sheetId="4" r:id="rId4"/>
-    <sheet name="demographic_profiles" sheetId="5" r:id="rId5"/>
-    <sheet name="constants" sheetId="6" r:id="rId6"/>
+    <sheet name="settings" sheetId="1" r:id="rId1"/>
+    <sheet name="treatment" sheetId="2" r:id="rId2"/>
+    <sheet name="role" sheetId="3" r:id="rId3"/>
+    <sheet name="prompt" sheetId="4" r:id="rId4"/>
+    <sheet name="profile" sheetId="5" r:id="rId5"/>
+    <sheet name="constant" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">demographic_profiles!$A$1:$Y$5312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">profile!$A$1:$W$5312</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -33,10 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="205">
-  <si>
-    <t>experimental_setting</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="191">
   <si>
     <t>value</t>
   </si>
@@ -45,12 +42,6 @@
   </si>
   <si>
     <t>model_info</t>
-  </si>
-  <si>
-    <t>num_sessions</t>
-  </si>
-  <si>
-    <t>max_conversation_length</t>
   </si>
   <si>
     <t>treatment_assignment_strategy</t>
@@ -62,31 +53,16 @@
     <t>treatment</t>
   </si>
   <si>
-    <t>session_assignment_strategy</t>
-  </si>
-  <si>
     <t>role_assignment_strategy</t>
   </si>
   <si>
     <t>treatment_label</t>
   </si>
   <si>
-    <t>treatment_description</t>
-  </si>
-  <si>
     <t>role_label</t>
   </si>
   <si>
-    <t>role_description</t>
-  </si>
-  <si>
-    <t>task_id</t>
-  </si>
-  <si>
     <t>type</t>
-  </si>
-  <si>
-    <t>task_order</t>
   </si>
   <si>
     <t>is_adapted</t>
@@ -96,12 +72,6 @@
   </si>
   <si>
     <t>llm_text</t>
-  </si>
-  <si>
-    <t>var_name</t>
-  </si>
-  <si>
-    <t>var_type</t>
   </si>
   <si>
     <t>response_options</t>
@@ -128,13 +98,7 @@
     <t>ID</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>random_seed</t>
-  </si>
-  <si>
-    <t>session_column</t>
   </si>
   <si>
     <t>role_column</t>
@@ -150,9 +114,6 @@
   </si>
   <si>
     <t>private_question</t>
-  </si>
-  <si>
-    <t>include_backstories</t>
   </si>
   <si>
     <t>SubjectID</t>
@@ -207,12 +168,6 @@
   </si>
   <si>
     <t>p_i_Q91</t>
-  </si>
-  <si>
-    <t>vaccine_intention</t>
-  </si>
-  <si>
-    <t>vaccine_reasons_no</t>
   </si>
   <si>
     <t>vaccine_chance</t>
@@ -278,12 +233,6 @@
     <t>Do you have a registered mobile number?</t>
   </si>
   <si>
-    <t>Do you think you will get a first shot of a COVID-19 vaccine within the first 6 weeks after the vaccine becomes available to you?</t>
-  </si>
-  <si>
-    <t>Why will you NOT get vaccinated against COVID-19?</t>
-  </si>
-  <si>
     <t>We understand that there is always some uncertainty regarding all decisions. From 0% to 100%, what do you think are the chances that you will choose to get a first shot of a COVID-19 vaccine within the first 6 weeks after the vaccine becomes available to you? - 4</t>
   </si>
   <si>
@@ -329,9 +278,6 @@
     <t>No, I do not have a mobile number where I can get paid</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>High Cash</t>
   </si>
   <si>
@@ -345,12 +291,6 @@
   </si>
   <si>
     <t>Good</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>I am concerned about dangerous side effects from the COVID-19 vaccine</t>
   </si>
   <si>
     <t>CDC Health</t>
@@ -386,9 +326,6 @@
     <t>Very good</t>
   </si>
   <si>
-    <t>I don't believe the COVID-19 vaccine will be effective, I am concerned about dangerous side effects from the COVID-19 vaccine</t>
-  </si>
-  <si>
     <t>Never</t>
   </si>
   <si>
@@ -404,9 +341,6 @@
     <t>Employed (part time)</t>
   </si>
   <si>
-    <t>Other</t>
-  </si>
-  <si>
     <t>Very bad</t>
   </si>
   <si>
@@ -420,9 +354,6 @@
   </si>
   <si>
     <t>Retired</t>
-  </si>
-  <si>
-    <t>I cannot be vaccinated due to medical reasons as advised by a doctor, Other</t>
   </si>
   <si>
     <t>Student</t>
@@ -452,16 +383,10 @@
     <t>FOSUANSA 2</t>
   </si>
   <si>
-    <t>I am a pregnant/nursing mother and cannot be vaccinated, I am concerned about dangerous side effects from the COVID-19 vaccine</t>
-  </si>
-  <si>
     <t>ANKAASE</t>
   </si>
   <si>
     <t>ZAMBOREE</t>
-  </si>
-  <si>
-    <t>I cannot be vaccinated due to medical reasons as advised by a doctor, I am concerned about dangerous side effects from the COVID-19 vaccine</t>
   </si>
   <si>
     <t>Asesewa Community D</t>
@@ -482,9 +407,6 @@
     <t>Kyeaboso</t>
   </si>
   <si>
-    <t>The COVID-19 virus will not be very harmful to my health</t>
-  </si>
-  <si>
     <t>SABINA</t>
   </si>
   <si>
@@ -495,9 +417,6 @@
   </si>
   <si>
     <t>KUNTANASE 2</t>
-  </si>
-  <si>
-    <t>The COVID-19 virus will not be very harmful to my health, Other</t>
   </si>
   <si>
     <t>ESHIEM ODUMASI</t>
@@ -518,16 +437,10 @@
     <t>Kotokye</t>
   </si>
   <si>
-    <t>I am a pregnant/nursing mother and cannot be vaccinated</t>
-  </si>
-  <si>
     <t>DANSAME</t>
   </si>
   <si>
     <t>KORANKYI</t>
-  </si>
-  <si>
-    <t>I am concerned about dangerous side effects from the COVID-19 vaccine, I don't trust the health care providers in this country</t>
   </si>
   <si>
     <t>Vocational/Technical/Commercial</t>
@@ -572,19 +485,10 @@
     <t>JAMRA</t>
   </si>
   <si>
-    <t>gpt-4.1</t>
-  </si>
-  <si>
     <t>random</t>
   </si>
   <si>
     <t>Respond to each question in the exact format specified and do not add any information beyond what is requested.</t>
-  </si>
-  <si>
-    <t>Have you received a COVID-19 vaccine? {response_options}</t>
-  </si>
-  <si>
-    <t>Have you actually received a COVID-19 vaccine and can this be verified in the records of the Ghanaian District Health Offices? {response_options}</t>
   </si>
   <si>
     <t>vaccination_qn_1</t>
@@ -599,18 +503,6 @@
     <t>hf_inference_endpoint</t>
   </si>
   <si>
-    <t>Assume the role of a facilitator in a public good experiment.</t>
-  </si>
-  <si>
-    <t>Facilitator</t>
-  </si>
-  <si>
-    <t>num_subjects_per_session</t>
-  </si>
-  <si>
-    <t>session</t>
-  </si>
-  <si>
     <t>role</t>
   </si>
   <si>
@@ -621,21 +513,6 @@
   </si>
   <si>
     <t>participant_label</t>
-  </si>
-  <si>
-    <t>Please put yourself in the shoes of a human {{participant_label}} participating in a healthcare survey in Ghana about the COVID-19 vaccine. You will be provided with a demographic profile that describes your age, gender, highest education level you achieved, region/district you live in, size of your village, distance to nearest health clinic in km, household size, current employment situation, average household spending, household economic/financial condition, number of family members and friends in another village, social network, social media use, and vaccination intention. The information will be provided to you in the format of a survey interview. You will see a question from the “Interviewer:” and then your human {{participant_label}} response will be preceded by “Me:”. Lastly, you will watch a video and receive further information on the vaccination intention of your human {{participant_label}}. Thereafter, you will be asked whether you received the COVID-19 vaccination. Please provide a consistent and coherent response using all the information provided. It is crucial for you to accurately replicate the response of a human {{participant_label}} that has the demographic profile you are provided. The human {{participant_label}} response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Respond to each question in the exact format specified and do not add any information beyond what is requested.</t>
-  </si>
-  <si>
-    <t>You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID 19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. Getting the COVID-19 vaccine will help prevent you from getting COVID-19 and reduce your risk of being hospitalized with COVID-19. COVID 19 vaccine help you to protect yourself your environment and your loved ones from COVID-19 exposure.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification</t>
-  </si>
-  <si>
-    <t>You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nThe Sun lights up our lives for business for education even for socializing but when the Sun sets many people use candles who are quality battery-operated torches and kerosene lamps as inefficient and expensive ways to create light. What if you can take some Sun with you at night?  You can with portable solar products there are different types, but each portable solar product is made up of three basic parts: a small solar panel, a modern rechargeable battery and an LED bulb. The solar panel catches the light from the Sun and stores this energy in the battery. This can now be used for much needed light when it's dark. Many can even charge phones portable solar products should be reliable affordable and warranted be sure to demand top quality solar products look for these products lighting Africa shining the way.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status.  If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification.</t>
-  </si>
-  <si>
-    <t>You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID-19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. If you have at least one COVID-19 vaccine shot you will receive 20 Cedi. If you get vaccinated, you will get rewarded.\n\nWe indicated that we will follow up with you in 30 days.  We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification and you will be paid your 20 Cedi via cell phone money payment or by cash if you prefer.</t>
-  </si>
-  <si>
-    <t>You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID-19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. If you have at least one COVID-19 vaccine shot you will receive 60 Cedi. If you get vaccinated, you will get rewarded.\n\nWe indicated that we will follow up with you in 6 weeks.  We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification and you will be paid your 60 Cedi via cell phone money payment or by cash if you prefer.</t>
   </si>
   <si>
     <t>["subject"]</t>
@@ -649,6 +526,99 @@
   <si>
     <t>Provide a short description of this photo: 
 https://images.squarespace-cdn.com/content/v1/607f89e638219e13eee71b1e/1684821560422-SD5V37BAG28BURTLIXUQ/michael-sum-LEpfefQf4rU-unsplash.jpg?format=2500w</t>
+  </si>
+  <si>
+    <t>group</t>
+  </si>
+  <si>
+    <t>session_setting</t>
+  </si>
+  <si>
+    <t>num_subjects_per_group</t>
+  </si>
+  <si>
+    <t>num_groups</t>
+  </si>
+  <si>
+    <t>group_assignment_strategy</t>
+  </si>
+  <si>
+    <t>group_column</t>
+  </si>
+  <si>
+    <t>build_profile_qna</t>
+  </si>
+  <si>
+    <t>build_profile_backstories</t>
+  </si>
+  <si>
+    <t>constant_label</t>
+  </si>
+  <si>
+    <t>{
+"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID 19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. Getting the COVID-19 vaccine will help prevent you from getting COVID-19 and reduce your risk of being hospitalized with COVID-19. COVID 19 vaccine help you to protect yourself your environment and your loved ones from COVID-19 exposure.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification"
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nThe Sun lights up our lives for business for education even for socializing but when the Sun sets many people use candles who are quality battery-operated torches and kerosene lamps as inefficient and expensive ways to create light. What if you can take some Sun with you at night?  You can with portable solar products there are different types, but each portable solar product is made up of three basic parts: a small solar panel, a modern rechargeable battery and an LED bulb. The solar panel catches the light from the Sun and stores this energy in the battery. This can now be used for much needed light when it's dark. Many can even charge phones portable solar products should be reliable affordable and warranted be sure to demand top quality solar products look for these products lighting Africa shining the way.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status.  If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID-19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. If you have at least one COVID-19 vaccine shot you will receive 20 Cedi. If you get vaccinated, you will get rewarded.\n\nWe indicated that we will follow up with you in 30 days.  We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification and you will be paid your 20 Cedi via cell phone money payment or by cash if you prefer."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID-19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. If you have at least one COVID-19 vaccine shot you will receive 60 Cedi. If you get vaccinated, you will get rewarded.\n\nWe indicated that we will follow up with you in 6 weeks.  We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification and you will be paid your 60 Cedi via cell phone money payment or by cash if you prefer."
+}</t>
+  </si>
+  <si>
+    <t>facilitator</t>
+  </si>
+  <si>
+    <t>participant</t>
+  </si>
+  <si>
+    <t>{
+"description":"Assume the role of a facilitator in a public good experiment."
+}</t>
+  </si>
+  <si>
+    <t>{
+"description":"Please put yourself in the shoes of a human {{ constant.participant_label }} participating in a healthcare survey in Ghana about the COVID-19 vaccine. You will be provided with a demographic profile that describes your age, gender, highest education level you achieved, region/district you live in, size of your village, distance to nearest health clinic in km, household size, current employment situation, average household spending, household economic/financial condition, number of family members and friends in another village, social network, social media use, and vaccination intention. The information will be provided to you in the format of a survey interview. You will see a question from the “Interviewer:” and then your human {{ constant.participant_label }} response will be preceded by “Me:”. Lastly, you will watch a video and receive further information on the vaccination intention of your human {{ constant.participant_label }}. Thereafter, you will be asked whether you received the COVID-19 vaccination. Please provide a consistent and coherent response using all the information provided. It is crucial for you to accurately replicate the response of a human {{ constant.participant_label }} that has the demographic profile you are provided. The human {{ constant.participant_label }} response will vary depending on their demographic profile. If you are unsure of an answer, provide a plausible response that is based on all of the information available to you. Respond to each question in the exact format specified and do not add any information beyond what is requested."
+}</t>
+  </si>
+  <si>
+    <t>Have you received a COVID-19 vaccine? {{ response_options }}</t>
+  </si>
+  <si>
+    <t>Have you actually received a COVID-19 vaccine and can this be verified in the records of the Ghanaian District Health Offices? {{ response_options }}</t>
+  </si>
+  <si>
+    <t>round_id</t>
+  </si>
+  <si>
+    <t>round_order</t>
+  </si>
+  <si>
+    <t>response_name</t>
+  </si>
+  <si>
+    <t>response_type</t>
+  </si>
+  <si>
+    <t>gpt-5-mini</t>
+  </si>
+  <si>
+    <t>{{ treatment.description }}</t>
+  </si>
+  <si>
+    <t>treatment_description</t>
+  </si>
+  <si>
+    <t>max_num_rounds</t>
   </si>
 </sst>
 </file>
@@ -947,37 +917,37 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -985,7 +955,7 @@
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -993,7 +963,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>167</v>
       </c>
       <c r="B7" s="2">
         <v>45</v>
@@ -1001,60 +971,60 @@
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="2">
         <v>5</v>
-      </c>
-      <c r="B8" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>169</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B15" s="3">
         <v>42</v>
@@ -1062,28 +1032,35 @@
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>39</v>
+        <v>170</v>
       </c>
       <c r="B16" s="3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="19" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="20" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="25" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="28" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="30" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="32" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2072,7 +2049,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose a role assignment strategy from the dropdown list." sqref="B13" xr:uid="{CD5A8A2F-647C-7140-A110-46420E7F8C2F}">
       <formula1>"random, manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B16" xr:uid="{E2415674-B0C6-6543-8726-22265FD96C3A}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B16:B17" xr:uid="{E2415674-B0C6-6543-8726-22265FD96C3A}">
       <formula1>"True, False"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please input an integer greater than 1." sqref="B6" xr:uid="{9377BD74-7833-D542-BA3D-AF885CDF2E49}">
@@ -2089,49 +2066,50 @@
   <dimension ref="A1:B1000"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="14.1640625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="3" customWidth="1"/>
     <col min="3" max="27" width="10.6640625" style="3" customWidth="1"/>
     <col min="28" max="16384" width="11.1640625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3149,26 +3127,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>177</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4172,7 +4150,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M847"/>
+  <dimension ref="A1:M848"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -4194,43 +4172,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4238,7 +4216,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -4247,16 +4225,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="3" t="b">
@@ -4277,7 +4255,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -4285,32 +4263,30 @@
       <c r="D3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>182</v>
+      <c r="E3" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>188</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I3" s="1"/>
       <c r="J3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M3" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4318,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -4327,19 +4303,19 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>185</v>
+        <v>152</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>186</v>
+        <v>154</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -4355,48 +4331,88 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="3">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="3">
+        <v>26</v>
+      </c>
+      <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>203</v>
+      <c r="E5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>202</v>
+        <v>19</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="J5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" s="3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="7"/>
-    </row>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E8" s="7"/>
+    </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5236,19 +5252,20 @@
     <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="D2:D1048576 J2:M1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
       <formula1>"True, False"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B2:B1048576" xr:uid="{04E1F09C-E3CF-9344-AD18-370A7D398746}">
-      <formula1>"context, public_question, private_question, discussion"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H3 H5:H1048576" xr:uid="{B52963B2-1D08-9B4B-A4B6-B266870FC6FB}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H4 H6:H1048576" xr:uid="{B52963B2-1D08-9B4B-A4B6-B266870FC6FB}">
       <formula1>"context, category, integer, free-text"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H4" xr:uid="{2FDB2F7E-ECDB-E740-A5BE-8D2E81EF5F27}">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H5" xr:uid="{2FDB2F7E-ECDB-E740-A5BE-8D2E81EF5F27}">
       <formula1>"context, category, integer"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B2:B1048576" xr:uid="{01FAA86E-E699-014C-BF05-158DA893F695}">
+      <formula1>"context, discussion, public_question, repeat_public_question, private_question, repeat_private_question"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -5258,188 +5275,176 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:AA5312"/>
+  <dimension ref="A1:Y5312"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.5" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="10.5" customWidth="1"/>
-    <col min="21" max="21" width="16.6640625" customWidth="1"/>
-    <col min="22" max="41" width="10.5" customWidth="1"/>
+    <col min="4" max="18" width="10.5" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
+    <col min="20" max="39" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
         <v>40</v>
       </c>
-      <c r="B1" t="s">
+      <c r="O1" t="s">
         <v>41</v>
       </c>
-      <c r="C1" t="s">
+      <c r="P1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" t="s">
+      <c r="Q1" t="s">
         <v>43</v>
       </c>
-      <c r="E1" t="s">
+      <c r="R1" t="s">
         <v>44</v>
       </c>
-      <c r="F1" t="s">
+      <c r="S1" t="s">
         <v>45</v>
       </c>
-      <c r="G1" t="s">
+      <c r="T1" t="s">
         <v>46</v>
       </c>
-      <c r="H1" t="s">
+      <c r="U1" t="s">
         <v>47</v>
       </c>
-      <c r="I1" t="s">
+      <c r="V1" t="s">
         <v>48</v>
       </c>
-      <c r="J1" t="s">
+      <c r="W1" t="s">
         <v>49</v>
       </c>
-      <c r="K1" t="s">
+      <c r="X1" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="6" customFormat="1" ht="289" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L1" t="s">
+      <c r="D2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="M1" t="s">
+      <c r="E2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="N1" t="s">
+      <c r="F2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="O1" t="s">
+      <c r="G2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="P1" t="s">
+      <c r="H2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="I2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="R1" t="s">
+      <c r="J2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="S1" t="s">
+      <c r="K2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T1" t="s">
+      <c r="L2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="U1" t="s">
+      <c r="M2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="V1" t="s">
+      <c r="N2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="W1" t="s">
+      <c r="O2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="X1" t="s">
+      <c r="P2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Q2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="Z1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="6" customFormat="1" ht="289" x14ac:dyDescent="0.2">
-      <c r="A2" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="I2" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="X2" s="6" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2060</v>
       </c>
       <c r="B3" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C3" s="5">
         <v>44602.341666666667</v>
@@ -5448,19 +5453,19 @@
         <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="J3">
         <v>1578</v>
@@ -5475,7 +5480,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O3">
         <v>170</v>
@@ -5484,30 +5489,27 @@
         <v>10</v>
       </c>
       <c r="Q3" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R3" t="s">
-        <v>109</v>
-      </c>
-      <c r="S3" t="s">
-        <v>98</v>
-      </c>
-      <c r="U3">
+        <v>89</v>
+      </c>
+      <c r="S3">
         <v>74</v>
       </c>
-      <c r="Z3">
+      <c r="X3">
         <v>1</v>
       </c>
-      <c r="AA3" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>4717</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C4" s="5">
         <v>44610.254861111112</v>
@@ -5516,19 +5518,19 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" t="s">
         <v>91</v>
       </c>
-      <c r="F4" t="s">
-        <v>110</v>
-      </c>
-      <c r="G4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" t="s">
-        <v>111</v>
-      </c>
       <c r="I4" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="J4">
         <v>246</v>
@@ -5543,7 +5545,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O4">
         <v>150</v>
@@ -5552,33 +5554,27 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R4" t="s">
-        <v>109</v>
-      </c>
-      <c r="S4" t="s">
-        <v>104</v>
-      </c>
-      <c r="T4" t="s">
-        <v>105</v>
-      </c>
-      <c r="U4">
+        <v>89</v>
+      </c>
+      <c r="S4">
         <v>40</v>
       </c>
-      <c r="Z4">
+      <c r="X4">
         <v>2</v>
       </c>
-      <c r="AA4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>6393</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C5" s="5">
         <v>44618.104861111111</v>
@@ -5587,19 +5583,19 @@
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F5" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H5" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="J5">
         <v>215</v>
@@ -5614,7 +5610,7 @@
         <v>4</v>
       </c>
       <c r="N5" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O5">
         <v>360</v>
@@ -5623,45 +5619,39 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R5" t="s">
-        <v>109</v>
-      </c>
-      <c r="S5" t="s">
-        <v>104</v>
-      </c>
-      <c r="T5" t="s">
-        <v>117</v>
+        <v>89</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>4</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>4</v>
-      </c>
-      <c r="W5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="W5" t="s">
+        <v>97</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
       <c r="Y5" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z5">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1648</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C6" s="5">
         <v>44601.211805555555</v>
@@ -5670,19 +5660,19 @@
         <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F6" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G6" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="J6">
         <v>610</v>
@@ -5697,7 +5687,7 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O6">
         <v>150</v>
@@ -5706,30 +5696,27 @@
         <v>20</v>
       </c>
       <c r="Q6" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R6" t="s">
-        <v>109</v>
-      </c>
-      <c r="S6" t="s">
-        <v>98</v>
-      </c>
-      <c r="U6">
+        <v>89</v>
+      </c>
+      <c r="S6">
         <v>100</v>
       </c>
-      <c r="Z6">
+      <c r="X6">
         <v>4</v>
       </c>
-      <c r="AA6" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2891</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C7" s="5">
         <v>44605.447916666664</v>
@@ -5738,19 +5725,19 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H7" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I7" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="J7">
         <v>1176</v>
@@ -5765,7 +5752,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O7">
         <v>450</v>
@@ -5774,30 +5761,27 @@
         <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R7" t="s">
-        <v>109</v>
-      </c>
-      <c r="S7" t="s">
-        <v>98</v>
-      </c>
-      <c r="U7">
+        <v>89</v>
+      </c>
+      <c r="S7">
         <v>97</v>
       </c>
-      <c r="Z7">
+      <c r="X7">
         <v>5</v>
       </c>
-      <c r="AA7" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>6796</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C8" s="5">
         <v>44618.053472222222</v>
@@ -5806,19 +5790,19 @@
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G8" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I8" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="J8">
         <v>215</v>
@@ -5833,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="O8">
         <v>60</v>
@@ -5842,33 +5826,27 @@
         <v>80</v>
       </c>
       <c r="Q8" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R8" t="s">
-        <v>97</v>
-      </c>
-      <c r="S8" t="s">
-        <v>104</v>
-      </c>
-      <c r="T8" t="s">
-        <v>129</v>
-      </c>
-      <c r="U8">
+        <v>80</v>
+      </c>
+      <c r="S8">
         <v>18</v>
       </c>
-      <c r="Z8">
+      <c r="X8">
         <v>6</v>
       </c>
-      <c r="AA8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>4297</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C9" s="5">
         <v>44609.390972222223</v>
@@ -5877,19 +5855,19 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F9" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H9" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I9" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J9">
         <v>3838</v>
@@ -5904,7 +5882,7 @@
         <v>3</v>
       </c>
       <c r="N9" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O9">
         <v>120</v>
@@ -5913,33 +5891,30 @@
         <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R9" t="s">
-        <v>109</v>
-      </c>
-      <c r="S9" t="s">
-        <v>98</v>
-      </c>
-      <c r="U9">
+        <v>89</v>
+      </c>
+      <c r="S9">
         <v>9</v>
       </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
       <c r="X9">
-        <v>0</v>
-      </c>
-      <c r="Z9">
         <v>7</v>
       </c>
-      <c r="AA9" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y9" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1556</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C10" s="5">
         <v>44601.120833333334</v>
@@ -5948,19 +5923,19 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H10" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I10" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="J10">
         <v>3455</v>
@@ -5975,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O10">
         <v>35</v>
@@ -5984,30 +5959,27 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R10" t="s">
-        <v>109</v>
-      </c>
-      <c r="S10" t="s">
-        <v>98</v>
-      </c>
-      <c r="U10">
+        <v>89</v>
+      </c>
+      <c r="S10">
         <v>88</v>
       </c>
-      <c r="Z10">
+      <c r="X10">
         <v>8</v>
       </c>
-      <c r="AA10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y10" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5922</v>
       </c>
       <c r="B11" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C11" s="5">
         <v>44617.210416666669</v>
@@ -6016,19 +5988,19 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I11" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="J11">
         <v>731</v>
@@ -6043,7 +6015,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="O11">
         <v>140</v>
@@ -6052,36 +6024,33 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R11" t="s">
-        <v>109</v>
-      </c>
-      <c r="S11" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S11">
+        <v>50</v>
       </c>
       <c r="U11">
-        <v>50</v>
-      </c>
-      <c r="W11">
         <v>10</v>
       </c>
+      <c r="V11">
+        <v>4</v>
+      </c>
       <c r="X11">
-        <v>4</v>
-      </c>
-      <c r="Z11">
         <v>9</v>
       </c>
-      <c r="AA11" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y11" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1694</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C12" s="5">
         <v>44601.181944444441</v>
@@ -6090,19 +6059,19 @@
         <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I12" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="J12">
         <v>3538</v>
@@ -6117,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O12">
         <v>200</v>
@@ -6126,45 +6095,39 @@
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R12" t="s">
-        <v>109</v>
-      </c>
-      <c r="S12" t="s">
-        <v>104</v>
-      </c>
-      <c r="T12" t="s">
-        <v>139</v>
+        <v>89</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V12">
-        <v>6</v>
-      </c>
-      <c r="W12">
-        <v>4</v>
+        <v>16</v>
+      </c>
+      <c r="W12" t="s">
+        <v>97</v>
       </c>
       <c r="X12">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z12">
-        <v>10</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1707</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C13" s="5">
         <v>44601.337500000001</v>
@@ -6173,19 +6136,19 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H13" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I13" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
       <c r="J13">
         <v>318</v>
@@ -6200,7 +6163,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O13">
         <v>200</v>
@@ -6209,30 +6172,27 @@
         <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R13" t="s">
-        <v>109</v>
-      </c>
-      <c r="S13" t="s">
-        <v>98</v>
-      </c>
-      <c r="U13">
+        <v>89</v>
+      </c>
+      <c r="S13">
         <v>100</v>
       </c>
-      <c r="Z13">
+      <c r="X13">
         <v>11</v>
       </c>
-      <c r="AA13" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y13" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>4009</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C14" s="5">
         <v>44608.175694444442</v>
@@ -6241,19 +6201,19 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I14" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="J14">
         <v>128</v>
@@ -6268,7 +6228,7 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O14">
         <v>210</v>
@@ -6277,33 +6237,27 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R14" t="s">
-        <v>109</v>
-      </c>
-      <c r="S14" t="s">
-        <v>104</v>
-      </c>
-      <c r="T14" t="s">
-        <v>142</v>
-      </c>
-      <c r="U14">
+        <v>89</v>
+      </c>
+      <c r="S14">
         <v>100</v>
       </c>
-      <c r="Z14">
+      <c r="X14">
         <v>12</v>
       </c>
-      <c r="AA14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y14" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>6443</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C15" s="5">
         <v>44618.205555555556</v>
@@ -6312,19 +6266,19 @@
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H15" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I15" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="J15">
         <v>2510</v>
@@ -6339,7 +6293,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O15">
         <v>60</v>
@@ -6348,42 +6302,39 @@
         <v>10</v>
       </c>
       <c r="Q15" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R15" t="s">
-        <v>109</v>
-      </c>
-      <c r="S15" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S15">
+        <v>62</v>
+      </c>
+      <c r="T15">
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="V15">
-        <v>6</v>
-      </c>
-      <c r="W15">
-        <v>4</v>
+        <v>23</v>
+      </c>
+      <c r="W15" t="s">
+        <v>97</v>
       </c>
       <c r="X15">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="Y15" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z15">
-        <v>13</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5680</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C16" s="5">
         <v>44615.270833333336</v>
@@ -6392,19 +6343,19 @@
         <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I16" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="J16">
         <v>633</v>
@@ -6419,7 +6370,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O16">
         <v>280</v>
@@ -6428,42 +6379,39 @@
         <v>70</v>
       </c>
       <c r="Q16" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R16" t="s">
-        <v>109</v>
-      </c>
-      <c r="S16" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S16">
+        <v>30</v>
+      </c>
+      <c r="T16">
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="V16">
-        <v>8</v>
-      </c>
-      <c r="W16">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="W16" t="s">
+        <v>97</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Y16" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z16">
-        <v>14</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>4924</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C17" s="5">
         <v>44613.43472222222</v>
@@ -6472,19 +6420,19 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I17" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="J17">
         <v>706</v>
@@ -6499,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O17">
         <v>35</v>
@@ -6508,30 +6456,27 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R17" t="s">
-        <v>109</v>
-      </c>
-      <c r="S17" t="s">
-        <v>98</v>
-      </c>
-      <c r="U17">
+        <v>89</v>
+      </c>
+      <c r="S17">
         <v>70</v>
       </c>
-      <c r="Z17">
+      <c r="X17">
         <v>15</v>
       </c>
-      <c r="AA17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y17" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>3288</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C18" s="5">
         <v>44606.345138888886</v>
@@ -6540,19 +6485,19 @@
         <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F18" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H18" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I18" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="J18">
         <v>1581</v>
@@ -6567,7 +6512,7 @@
         <v>2</v>
       </c>
       <c r="N18" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O18">
         <v>200</v>
@@ -6576,42 +6521,39 @@
         <v>40</v>
       </c>
       <c r="Q18" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R18" t="s">
-        <v>109</v>
-      </c>
-      <c r="S18" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S18">
+        <v>82</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="V18">
         <v>0</v>
       </c>
-      <c r="W18">
-        <v>25</v>
+      <c r="W18" t="s">
+        <v>97</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Y18" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z18">
-        <v>16</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>3940</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C19" s="5">
         <v>44608.157638888886</v>
@@ -6620,19 +6562,19 @@
         <v>45</v>
       </c>
       <c r="E19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
+        <v>90</v>
+      </c>
+      <c r="G19" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
         <v>91</v>
       </c>
-      <c r="F19" t="s">
-        <v>110</v>
-      </c>
-      <c r="G19" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" t="s">
-        <v>111</v>
-      </c>
       <c r="I19" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="J19">
         <v>1454</v>
@@ -6647,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -6656,30 +6598,27 @@
         <v>20</v>
       </c>
       <c r="Q19" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R19" t="s">
-        <v>109</v>
-      </c>
-      <c r="S19" t="s">
-        <v>98</v>
-      </c>
-      <c r="U19">
+        <v>89</v>
+      </c>
+      <c r="S19">
         <v>72</v>
       </c>
-      <c r="Z19">
+      <c r="X19">
         <v>17</v>
       </c>
-      <c r="AA19" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>3140</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C20" s="5">
         <v>44605.251388888886</v>
@@ -6688,19 +6627,19 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H20" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I20" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="J20">
         <v>1498</v>
@@ -6715,7 +6654,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O20">
         <v>50</v>
@@ -6724,33 +6663,27 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R20" t="s">
-        <v>109</v>
-      </c>
-      <c r="S20" t="s">
-        <v>104</v>
-      </c>
-      <c r="T20" t="s">
-        <v>149</v>
-      </c>
-      <c r="U20">
+        <v>89</v>
+      </c>
+      <c r="S20">
         <v>50</v>
       </c>
-      <c r="Z20">
+      <c r="X20">
         <v>18</v>
       </c>
-      <c r="AA20" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y20" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>4106</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C21" s="5">
         <v>44608.160416666666</v>
@@ -6759,19 +6692,19 @@
         <v>31</v>
       </c>
       <c r="E21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" t="s">
         <v>91</v>
       </c>
-      <c r="F21" t="s">
-        <v>92</v>
-      </c>
-      <c r="G21" t="s">
-        <v>101</v>
-      </c>
-      <c r="H21" t="s">
-        <v>111</v>
-      </c>
       <c r="I21" t="s">
-        <v>150</v>
+        <v>124</v>
       </c>
       <c r="J21">
         <v>834</v>
@@ -6786,7 +6719,7 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O21">
         <v>350</v>
@@ -6795,42 +6728,39 @@
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R21" t="s">
-        <v>109</v>
-      </c>
-      <c r="S21" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S21">
+        <v>34</v>
+      </c>
+      <c r="T21">
+        <v>20</v>
       </c>
       <c r="U21">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>20</v>
-      </c>
-      <c r="W21">
-        <v>7</v>
+        <v>3</v>
+      </c>
+      <c r="W21" t="s">
+        <v>97</v>
       </c>
       <c r="X21">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="Y21" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z21">
-        <v>19</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1458</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C22" s="5">
         <v>44600.42083333333</v>
@@ -6839,19 +6769,19 @@
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G22" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I22" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="J22">
         <v>2006</v>
@@ -6866,7 +6796,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O22">
         <v>300</v>
@@ -6875,42 +6805,39 @@
         <v>7000</v>
       </c>
       <c r="Q22" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R22" t="s">
-        <v>109</v>
-      </c>
-      <c r="S22" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+      <c r="T22">
+        <v>1</v>
       </c>
       <c r="U22">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>1</v>
-      </c>
-      <c r="W22">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="W22" t="s">
+        <v>97</v>
       </c>
       <c r="X22">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y22" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z22">
-        <v>20</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2149</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C23" s="5">
         <v>44602.234027777777</v>
@@ -6919,19 +6846,19 @@
         <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F23" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G23" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H23" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I23" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="J23">
         <v>3510</v>
@@ -6946,7 +6873,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -6955,42 +6882,36 @@
         <v>15</v>
       </c>
       <c r="Q23" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R23" t="s">
-        <v>109</v>
-      </c>
-      <c r="S23" t="s">
-        <v>104</v>
-      </c>
-      <c r="T23" t="s">
-        <v>154</v>
-      </c>
-      <c r="U23">
+        <v>89</v>
+      </c>
+      <c r="S23">
         <v>0</v>
       </c>
+      <c r="T23">
+        <v>12</v>
+      </c>
       <c r="V23">
-        <v>12</v>
+        <v>10</v>
+      </c>
+      <c r="W23" t="s">
+        <v>97</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="Y23" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z23">
-        <v>21</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>415</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C24" s="5">
         <v>44597.34652777778</v>
@@ -6999,19 +6920,19 @@
         <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F24" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G24" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H24" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I24" t="s">
-        <v>155</v>
+        <v>128</v>
       </c>
       <c r="J24">
         <v>1736</v>
@@ -7026,7 +6947,7 @@
         <v>4</v>
       </c>
       <c r="N24" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O24">
         <v>170</v>
@@ -7035,33 +6956,27 @@
         <v>50</v>
       </c>
       <c r="Q24" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R24" t="s">
-        <v>97</v>
-      </c>
-      <c r="S24" t="s">
-        <v>104</v>
-      </c>
-      <c r="T24" t="s">
-        <v>105</v>
-      </c>
-      <c r="U24">
+        <v>80</v>
+      </c>
+      <c r="S24">
         <v>11</v>
       </c>
-      <c r="Z24">
+      <c r="X24">
         <v>22</v>
       </c>
-      <c r="AA24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y24" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>4785</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C25" s="5">
         <v>44613.245138888888</v>
@@ -7070,19 +6985,19 @@
         <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I25" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
       <c r="J25">
         <v>175</v>
@@ -7097,7 +7012,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O25">
         <v>150</v>
@@ -7106,30 +7021,27 @@
         <v>50</v>
       </c>
       <c r="Q25" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R25" t="s">
-        <v>109</v>
-      </c>
-      <c r="S25" t="s">
-        <v>98</v>
-      </c>
-      <c r="U25">
+        <v>89</v>
+      </c>
+      <c r="S25">
         <v>100</v>
       </c>
-      <c r="Z25">
+      <c r="X25">
         <v>23</v>
       </c>
-      <c r="AA25" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>4134</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C26" s="5">
         <v>44609.234027777777</v>
@@ -7138,19 +7050,19 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
         <v>91</v>
       </c>
-      <c r="F26" t="s">
-        <v>92</v>
-      </c>
-      <c r="G26" t="s">
-        <v>101</v>
-      </c>
-      <c r="H26" t="s">
-        <v>111</v>
-      </c>
       <c r="I26" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="J26">
         <v>695</v>
@@ -7165,7 +7077,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O26">
         <v>210</v>
@@ -7174,30 +7086,27 @@
         <v>15</v>
       </c>
       <c r="Q26" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R26" t="s">
-        <v>97</v>
-      </c>
-      <c r="S26" t="s">
-        <v>98</v>
-      </c>
-      <c r="U26">
+        <v>80</v>
+      </c>
+      <c r="S26">
         <v>65</v>
       </c>
-      <c r="Z26">
+      <c r="X26">
         <v>24</v>
       </c>
-      <c r="AA26" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y26" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>6489</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C27" s="5">
         <v>44618.247916666667</v>
@@ -7206,19 +7115,19 @@
         <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G27" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I27" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J27">
         <v>407</v>
@@ -7233,7 +7142,7 @@
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O27">
         <v>210</v>
@@ -7242,30 +7151,27 @@
         <v>70</v>
       </c>
       <c r="Q27" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R27" t="s">
-        <v>109</v>
-      </c>
-      <c r="S27" t="s">
-        <v>98</v>
-      </c>
-      <c r="U27">
+        <v>89</v>
+      </c>
+      <c r="S27">
         <v>5</v>
       </c>
-      <c r="Z27">
+      <c r="X27">
         <v>25</v>
       </c>
-      <c r="AA27" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y27" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1526</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C28" s="5">
         <v>44600.460416666669</v>
@@ -7274,19 +7180,19 @@
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F28" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H28" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I28" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="J28">
         <v>4422</v>
@@ -7301,7 +7207,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O28">
         <v>210</v>
@@ -7310,30 +7216,27 @@
         <v>40</v>
       </c>
       <c r="Q28" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R28" t="s">
-        <v>97</v>
-      </c>
-      <c r="S28" t="s">
-        <v>98</v>
-      </c>
-      <c r="U28">
+        <v>80</v>
+      </c>
+      <c r="S28">
         <v>83</v>
       </c>
-      <c r="Z28">
+      <c r="X28">
         <v>26</v>
       </c>
-      <c r="AA28" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>3093</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C29" s="5">
         <v>44605.17083333333</v>
@@ -7342,19 +7245,19 @@
         <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F29" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H29" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I29" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="J29">
         <v>1066</v>
@@ -7369,7 +7272,7 @@
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O29">
         <v>180</v>
@@ -7378,45 +7281,39 @@
         <v>140</v>
       </c>
       <c r="Q29" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R29" t="s">
-        <v>109</v>
-      </c>
-      <c r="S29" t="s">
-        <v>104</v>
-      </c>
-      <c r="T29" t="s">
-        <v>161</v>
+        <v>89</v>
+      </c>
+      <c r="S29">
+        <v>20</v>
+      </c>
+      <c r="T29">
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="V29">
-        <v>10</v>
-      </c>
-      <c r="W29">
-        <v>15</v>
+        <v>0</v>
+      </c>
+      <c r="W29" t="s">
+        <v>97</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Y29" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z29">
-        <v>27</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>4975</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C30" s="5">
         <v>44613.315972222219</v>
@@ -7425,19 +7322,19 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F30" t="s">
+        <v>112</v>
+      </c>
+      <c r="G30" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" t="s">
+        <v>113</v>
+      </c>
+      <c r="I30" t="s">
         <v>135</v>
-      </c>
-      <c r="G30" t="s">
-        <v>93</v>
-      </c>
-      <c r="H30" t="s">
-        <v>136</v>
-      </c>
-      <c r="I30" t="s">
-        <v>163</v>
       </c>
       <c r="J30">
         <v>167</v>
@@ -7452,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O30">
         <v>400</v>
@@ -7461,33 +7358,27 @@
         <v>30</v>
       </c>
       <c r="Q30" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R30" t="s">
-        <v>109</v>
-      </c>
-      <c r="S30" t="s">
-        <v>104</v>
-      </c>
-      <c r="T30" t="s">
-        <v>164</v>
-      </c>
-      <c r="U30">
+        <v>89</v>
+      </c>
+      <c r="S30">
         <v>10</v>
       </c>
-      <c r="Z30">
+      <c r="X30">
         <v>28</v>
       </c>
-      <c r="AA30" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y30" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2191</v>
       </c>
       <c r="B31" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C31" s="5">
         <v>44602.135416666664</v>
@@ -7496,19 +7387,19 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F31" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G31" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I31" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="J31">
         <v>1580</v>
@@ -7523,7 +7414,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O31">
         <v>200</v>
@@ -7532,42 +7423,39 @@
         <v>20</v>
       </c>
       <c r="Q31" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="R31" t="s">
-        <v>109</v>
-      </c>
-      <c r="S31" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S31">
+        <v>31</v>
+      </c>
+      <c r="T31">
+        <v>35</v>
       </c>
       <c r="U31">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="V31">
-        <v>35</v>
-      </c>
-      <c r="W31">
+        <v>100</v>
+      </c>
+      <c r="W31" t="s">
+        <v>138</v>
+      </c>
+      <c r="X31">
         <v>29</v>
       </c>
-      <c r="X31">
-        <v>100</v>
-      </c>
       <c r="Y31" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z31">
-        <v>29</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>538</v>
       </c>
       <c r="B32" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C32" s="5">
         <v>44597.540972222225</v>
@@ -7576,19 +7464,19 @@
         <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F32" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G32" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H32" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="I32" t="s">
-        <v>156</v>
+        <v>129</v>
       </c>
       <c r="J32">
         <v>1201</v>
@@ -7603,7 +7491,7 @@
         <v>3</v>
       </c>
       <c r="N32" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O32">
         <v>150</v>
@@ -7612,30 +7500,27 @@
         <v>15</v>
       </c>
       <c r="Q32" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R32" t="s">
-        <v>109</v>
-      </c>
-      <c r="S32" t="s">
-        <v>98</v>
-      </c>
-      <c r="U32">
+        <v>89</v>
+      </c>
+      <c r="S32">
         <v>100</v>
       </c>
-      <c r="Z32">
+      <c r="X32">
         <v>30</v>
       </c>
-      <c r="AA32" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>3679</v>
       </c>
       <c r="B33" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C33" s="5">
         <v>44606.201388888891</v>
@@ -7644,19 +7529,19 @@
         <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I33" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="J33">
         <v>1040</v>
@@ -7671,7 +7556,7 @@
         <v>5</v>
       </c>
       <c r="N33" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O33">
         <v>350</v>
@@ -7680,45 +7565,39 @@
         <v>180</v>
       </c>
       <c r="Q33" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="R33" t="s">
-        <v>109</v>
-      </c>
-      <c r="S33" t="s">
-        <v>104</v>
-      </c>
-      <c r="T33" t="s">
-        <v>123</v>
+        <v>89</v>
+      </c>
+      <c r="S33">
+        <v>51</v>
+      </c>
+      <c r="T33">
+        <v>14</v>
       </c>
       <c r="U33">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>14</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
+        <v>42</v>
+      </c>
+      <c r="W33" t="s">
+        <v>97</v>
       </c>
       <c r="X33">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="Y33" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z33">
-        <v>31</v>
-      </c>
-      <c r="AA33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>4806</v>
       </c>
       <c r="B34" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C34" s="5">
         <v>44613.434027777781</v>
@@ -7727,19 +7606,19 @@
         <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F34" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G34" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I34" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="J34">
         <v>1398</v>
@@ -7754,7 +7633,7 @@
         <v>4</v>
       </c>
       <c r="N34" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O34">
         <v>200</v>
@@ -7763,30 +7642,27 @@
         <v>20</v>
       </c>
       <c r="Q34" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R34" t="s">
-        <v>109</v>
-      </c>
-      <c r="S34" t="s">
-        <v>98</v>
-      </c>
-      <c r="U34">
+        <v>89</v>
+      </c>
+      <c r="S34">
         <v>71</v>
       </c>
-      <c r="Z34">
+      <c r="X34">
         <v>32</v>
       </c>
-      <c r="AA34" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="35" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y34" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>4604</v>
       </c>
       <c r="B35" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C35" s="5">
         <v>44610.093055555553</v>
@@ -7795,19 +7671,19 @@
         <v>68</v>
       </c>
       <c r="E35" t="s">
+        <v>74</v>
+      </c>
+      <c r="F35" t="s">
+        <v>112</v>
+      </c>
+      <c r="G35" t="s">
+        <v>83</v>
+      </c>
+      <c r="H35" t="s">
         <v>91</v>
       </c>
-      <c r="F35" t="s">
-        <v>135</v>
-      </c>
-      <c r="G35" t="s">
-        <v>101</v>
-      </c>
-      <c r="H35" t="s">
-        <v>111</v>
-      </c>
       <c r="I35" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="J35">
         <v>417</v>
@@ -7822,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -7831,30 +7707,27 @@
         <v>30</v>
       </c>
       <c r="Q35" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R35" t="s">
-        <v>97</v>
-      </c>
-      <c r="S35" t="s">
-        <v>98</v>
-      </c>
-      <c r="U35">
         <v>80</v>
       </c>
-      <c r="Z35">
+      <c r="S35">
+        <v>80</v>
+      </c>
+      <c r="X35">
         <v>33</v>
       </c>
-      <c r="AA35" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y35" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>4085</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C36" s="5">
         <v>44609.120138888888</v>
@@ -7863,19 +7736,19 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F36" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G36" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="J36">
         <v>855</v>
@@ -7890,7 +7763,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O36">
         <v>240</v>
@@ -7899,33 +7772,27 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R36" t="s">
-        <v>97</v>
-      </c>
-      <c r="S36" t="s">
-        <v>104</v>
-      </c>
-      <c r="T36" t="s">
-        <v>161</v>
-      </c>
-      <c r="U36">
+        <v>80</v>
+      </c>
+      <c r="S36">
         <v>100</v>
       </c>
-      <c r="Z36">
+      <c r="X36">
         <v>34</v>
       </c>
-      <c r="AA36" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y36" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2141</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C37" s="5">
         <v>44602.143750000003</v>
@@ -7934,19 +7801,19 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G37" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="J37">
         <v>3510</v>
@@ -7961,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O37">
         <v>350</v>
@@ -7970,30 +7837,27 @@
         <v>15</v>
       </c>
       <c r="Q37" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R37" t="s">
-        <v>109</v>
-      </c>
-      <c r="S37" t="s">
-        <v>98</v>
-      </c>
-      <c r="U37">
+        <v>89</v>
+      </c>
+      <c r="S37">
         <v>100</v>
       </c>
-      <c r="Z37">
+      <c r="X37">
         <v>35</v>
       </c>
-      <c r="AA37" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y37" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3794</v>
       </c>
       <c r="B38" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C38" s="5">
         <v>44608.310416666667</v>
@@ -8002,19 +7866,19 @@
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H38" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I38" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="J38">
         <v>1465</v>
@@ -8029,7 +7893,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="O38">
         <v>140</v>
@@ -8038,30 +7902,27 @@
         <v>80</v>
       </c>
       <c r="Q38" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R38" t="s">
-        <v>97</v>
-      </c>
-      <c r="S38" t="s">
-        <v>98</v>
-      </c>
-      <c r="U38">
+        <v>80</v>
+      </c>
+      <c r="S38">
         <v>92</v>
       </c>
-      <c r="Z38">
+      <c r="X38">
         <v>36</v>
       </c>
-      <c r="AA38" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y38" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>3355</v>
       </c>
       <c r="B39" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C39" s="5">
         <v>44606.291666666664</v>
@@ -8070,19 +7931,19 @@
         <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F39" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H39" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I39" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="J39">
         <v>629</v>
@@ -8097,7 +7958,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O39">
         <v>55</v>
@@ -8106,30 +7967,27 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R39" t="s">
-        <v>109</v>
-      </c>
-      <c r="S39" t="s">
-        <v>98</v>
-      </c>
-      <c r="U39">
+        <v>89</v>
+      </c>
+      <c r="S39">
         <v>91</v>
       </c>
-      <c r="Z39">
+      <c r="X39">
         <v>37</v>
       </c>
-      <c r="AA39" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="40" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y39" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1736</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C40" s="5">
         <v>44601.129166666666</v>
@@ -8138,19 +7996,19 @@
         <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F40" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G40" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H40" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I40" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="J40">
         <v>714</v>
@@ -8165,7 +8023,7 @@
         <v>4</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -8174,42 +8032,39 @@
         <v>45</v>
       </c>
       <c r="Q40" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R40" t="s">
-        <v>109</v>
-      </c>
-      <c r="S40" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S40">
+        <v>90</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
       </c>
       <c r="U40">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="V40">
-        <v>0</v>
-      </c>
-      <c r="W40">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="W40" t="s">
+        <v>97</v>
       </c>
       <c r="X40">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="Y40" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z40">
-        <v>38</v>
-      </c>
-      <c r="AA40" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="41" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>5144</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C41" s="5">
         <v>44614.393750000003</v>
@@ -8218,19 +8073,19 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F41" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G41" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I41" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="J41">
         <v>235</v>
@@ -8245,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O41">
         <v>210</v>
@@ -8254,42 +8109,39 @@
         <v>50</v>
       </c>
       <c r="Q41" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R41" t="s">
-        <v>109</v>
-      </c>
-      <c r="S41" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S41">
+        <v>100</v>
+      </c>
+      <c r="T41">
+        <v>10</v>
       </c>
       <c r="U41">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V41">
         <v>10</v>
       </c>
-      <c r="W41">
-        <v>0</v>
+      <c r="W41" t="s">
+        <v>138</v>
       </c>
       <c r="X41">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="Y41" t="s">
-        <v>167</v>
-      </c>
-      <c r="Z41">
-        <v>39</v>
-      </c>
-      <c r="AA41" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>4497</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C42" s="5">
         <v>44609.114583333336</v>
@@ -8298,19 +8150,19 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H42" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I42" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="J42">
         <v>984</v>
@@ -8325,7 +8177,7 @@
         <v>3</v>
       </c>
       <c r="N42" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O42">
         <v>300</v>
@@ -8334,30 +8186,27 @@
         <v>10</v>
       </c>
       <c r="Q42" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R42" t="s">
-        <v>109</v>
-      </c>
-      <c r="S42" t="s">
-        <v>98</v>
-      </c>
-      <c r="U42">
+        <v>89</v>
+      </c>
+      <c r="S42">
         <v>91</v>
       </c>
-      <c r="Z42">
+      <c r="X42">
         <v>40</v>
       </c>
-      <c r="AA42" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="43" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y42" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>3483</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C43" s="5">
         <v>44606.379861111112</v>
@@ -8366,19 +8215,19 @@
         <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="G43" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H43" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I43" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="J43">
         <v>296</v>
@@ -8393,7 +8242,7 @@
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="O43">
         <v>35</v>
@@ -8402,30 +8251,27 @@
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="R43" t="s">
-        <v>109</v>
-      </c>
-      <c r="S43" t="s">
-        <v>98</v>
-      </c>
-      <c r="U43">
+        <v>89</v>
+      </c>
+      <c r="S43">
         <v>76</v>
       </c>
-      <c r="Z43">
+      <c r="X43">
         <v>41</v>
       </c>
-      <c r="AA43" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y43" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>6450</v>
       </c>
       <c r="B44" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C44" s="5">
         <v>44618.227083333331</v>
@@ -8434,19 +8280,19 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F44" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="G44" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="H44" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="I44" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="J44">
         <v>407</v>
@@ -8461,7 +8307,7 @@
         <v>4</v>
       </c>
       <c r="N44" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O44">
         <v>100</v>
@@ -8470,30 +8316,27 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R44" t="s">
-        <v>97</v>
-      </c>
-      <c r="S44" t="s">
-        <v>98</v>
-      </c>
-      <c r="U44">
+        <v>80</v>
+      </c>
+      <c r="S44">
         <v>61</v>
       </c>
-      <c r="Z44">
+      <c r="X44">
         <v>42</v>
       </c>
-      <c r="AA44" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="45" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y44" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2882</v>
       </c>
       <c r="B45" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5">
         <v>44605.368750000001</v>
@@ -8502,19 +8345,19 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="I45" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="J45">
         <v>1176</v>
@@ -8529,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O45">
         <v>320</v>
@@ -8538,42 +8381,39 @@
         <v>40</v>
       </c>
       <c r="Q45" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R45" t="s">
-        <v>109</v>
-      </c>
-      <c r="S45" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S45">
+        <v>97</v>
+      </c>
+      <c r="T45">
+        <v>7</v>
       </c>
       <c r="U45">
+        <v>15</v>
+      </c>
+      <c r="V45">
+        <v>10</v>
+      </c>
+      <c r="W45" t="s">
         <v>97</v>
       </c>
-      <c r="V45">
-        <v>7</v>
-      </c>
-      <c r="W45">
-        <v>15</v>
-      </c>
       <c r="X45">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="Y45" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z45">
-        <v>43</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="46" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>4757</v>
       </c>
       <c r="B46" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C46" s="5">
         <v>44610.291666666664</v>
@@ -8582,19 +8422,19 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F46" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="I46" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="J46">
         <v>4620</v>
@@ -8609,7 +8449,7 @@
         <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O46">
         <v>300</v>
@@ -8618,42 +8458,39 @@
         <v>100</v>
       </c>
       <c r="Q46" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="R46" t="s">
-        <v>109</v>
-      </c>
-      <c r="S46" t="s">
-        <v>98</v>
+        <v>89</v>
+      </c>
+      <c r="S46">
+        <v>70</v>
+      </c>
+      <c r="T46">
+        <v>7</v>
       </c>
       <c r="U46">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="V46">
-        <v>7</v>
-      </c>
-      <c r="W46">
-        <v>6</v>
+        <v>26</v>
+      </c>
+      <c r="W46" t="s">
+        <v>126</v>
       </c>
       <c r="X46">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="Y46" t="s">
-        <v>152</v>
-      </c>
-      <c r="Z46">
-        <v>44</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1929</v>
       </c>
       <c r="B47" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C47" s="5">
         <v>44601.813194444447</v>
@@ -8662,19 +8499,19 @@
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="F47" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="H47" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="J47">
         <v>4995</v>
@@ -8689,7 +8526,7 @@
         <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="O47">
         <v>150</v>
@@ -8698,25 +8535,22 @@
         <v>30</v>
       </c>
       <c r="Q47" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="R47" t="s">
-        <v>109</v>
-      </c>
-      <c r="S47" t="s">
-        <v>98</v>
-      </c>
-      <c r="U47">
+        <v>89</v>
+      </c>
+      <c r="S47">
         <v>49</v>
       </c>
-      <c r="Z47">
+      <c r="X47">
         <v>45</v>
       </c>
-      <c r="AA47" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y47" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="5"/>
     </row>
     <row r="49" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24531,20 +24365,20 @@
     <col min="27" max="16384" width="11.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/demos/rct_experiment/rct_experiment_prompt_template.xlsx
+++ b/demos/rct_experiment/rct_experiment_prompt_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/rct_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DA868B-B4AB-C540-B89E-784649CCF537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A27529-10BF-B94E-A103-0BA731517645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="3760" windowWidth="34560" windowHeight="20140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="3760" windowWidth="34560" windowHeight="20140" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -33,12 +33,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="186">
   <si>
     <t>value</t>
-  </si>
-  <si>
-    <t>experiment_id</t>
   </si>
   <si>
     <t>model_info</t>
@@ -485,9 +482,6 @@
     <t>JAMRA</t>
   </si>
   <si>
-    <t>random</t>
-  </si>
-  <si>
     <t>Respond to each question in the exact format specified and do not add any information beyond what is requested.</t>
   </si>
   <si>
@@ -518,20 +512,7 @@
     <t>["subject"]</t>
   </si>
   <si>
-    <t>free-text</t>
-  </si>
-  <si>
-    <t>describe_image_thumbnail</t>
-  </si>
-  <si>
-    <t>Provide a short description of this photo: 
-https://images.squarespace-cdn.com/content/v1/607f89e638219e13eee71b1e/1684821560422-SD5V37BAG28BURTLIXUQ/michael-sum-LEpfefQf4rU-unsplash.jpg?format=2500w</t>
-  </si>
-  <si>
     <t>group</t>
-  </si>
-  <si>
-    <t>session_setting</t>
   </si>
   <si>
     <t>num_subjects_per_group</t>
@@ -578,9 +559,6 @@
     <t>facilitator</t>
   </si>
   <si>
-    <t>participant</t>
-  </si>
-  <si>
     <t>{
 "description":"Assume the role of a facilitator in a public good experiment."
 }</t>
@@ -619,6 +597,12 @@
   </si>
   <si>
     <t>max_num_rounds</t>
+  </si>
+  <si>
+    <t>settings_label</t>
+  </si>
+  <si>
+    <t>session_id</t>
   </si>
 </sst>
 </file>
@@ -917,7 +901,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -925,29 +909,29 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B4" s="7"/>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1">
         <v>0</v>
@@ -955,7 +939,7 @@
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B6" s="2">
         <v>1</v>
@@ -963,7 +947,7 @@
     </row>
     <row r="7" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B7" s="2">
         <v>45</v>
@@ -971,7 +955,7 @@
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
@@ -979,52 +963,55 @@
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="3">
         <v>42</v>
@@ -1032,15 +1019,15 @@
     </row>
     <row r="16" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B17" s="3" t="b">
         <v>0</v>
@@ -2074,7 +2061,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -2082,34 +2069,34 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3127,7 +3114,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -3135,18 +3122,18 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4150,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M848"/>
+  <dimension ref="A1:M847"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -4172,43 +4159,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4216,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2">
         <v>0</v>
@@ -4225,16 +4212,16 @@
         <v>0</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="3" t="b">
@@ -4255,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
@@ -4264,16 +4251,16 @@
         <v>0</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="3" t="b">
@@ -4294,7 +4281,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -4303,19 +4290,19 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>152</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>154</v>
       </c>
       <c r="J4" s="3" t="b">
         <v>1</v>
@@ -4335,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
@@ -4344,19 +4331,19 @@
         <v>0</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J5" s="3" t="b">
         <v>1</v>
@@ -4371,48 +4358,11 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="3">
-        <v>4</v>
-      </c>
-      <c r="D6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E8" s="7"/>
-    </row>
+    <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="11" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5252,17 +5202,16 @@
     <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="D2:D1048576 J2:M1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
-      <formula1>"True, False"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H4 H6:H1048576" xr:uid="{B52963B2-1D08-9B4B-A4B6-B266870FC6FB}">
       <formula1>"context, category, integer, free-text"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H5" xr:uid="{2FDB2F7E-ECDB-E740-A5BE-8D2E81EF5F27}">
       <formula1>"context, category, integer"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="J2:M1048576 D2:D1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
+      <formula1>"True, False"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="B2:B1048576" xr:uid="{01FAA86E-E699-014C-BF05-158DA893F695}">
       <formula1>"context, discussion, public_question, repeat_public_question, private_question, repeat_private_question"</formula1>
@@ -5287,156 +5236,156 @@
   <sheetData>
     <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>29</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>30</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>32</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>33</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>34</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>35</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>37</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>38</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>40</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>41</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>42</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>43</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>44</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>45</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>46</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>47</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>48</v>
       </c>
-      <c r="W1" t="s">
-        <v>49</v>
-      </c>
       <c r="X1" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="Y1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="6" customFormat="1" ht="289" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="I2" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="L2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="M2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="S2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="W2" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="W2" s="6" t="s">
-        <v>70</v>
-      </c>
       <c r="X2" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5444,7 +5393,7 @@
         <v>2060</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C3" s="5">
         <v>44602.341666666667</v>
@@ -5453,19 +5402,19 @@
         <v>36</v>
       </c>
       <c r="E3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I3" t="s">
         <v>87</v>
-      </c>
-      <c r="F3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I3" t="s">
-        <v>88</v>
       </c>
       <c r="J3">
         <v>1578</v>
@@ -5480,7 +5429,7 @@
         <v>3</v>
       </c>
       <c r="N3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O3">
         <v>170</v>
@@ -5489,10 +5438,10 @@
         <v>10</v>
       </c>
       <c r="Q3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S3">
         <v>74</v>
@@ -5501,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5509,7 +5458,7 @@
         <v>4717</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4" s="5">
         <v>44610.254861111112</v>
@@ -5518,19 +5467,19 @@
         <v>35</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G4" t="s">
+        <v>82</v>
+      </c>
+      <c r="H4" t="s">
         <v>90</v>
       </c>
-      <c r="G4" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>91</v>
-      </c>
-      <c r="I4" t="s">
-        <v>92</v>
       </c>
       <c r="J4">
         <v>246</v>
@@ -5545,7 +5494,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O4">
         <v>150</v>
@@ -5554,10 +5503,10 @@
         <v>0</v>
       </c>
       <c r="Q4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S4">
         <v>40</v>
@@ -5566,7 +5515,7 @@
         <v>2</v>
       </c>
       <c r="Y4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5574,7 +5523,7 @@
         <v>6393</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5" s="5">
         <v>44618.104861111111</v>
@@ -5583,19 +5532,19 @@
         <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G5" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" t="s">
+        <v>76</v>
+      </c>
+      <c r="I5" t="s">
         <v>94</v>
-      </c>
-      <c r="G5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" t="s">
-        <v>77</v>
-      </c>
-      <c r="I5" t="s">
-        <v>95</v>
       </c>
       <c r="J5">
         <v>215</v>
@@ -5610,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="N5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O5">
         <v>360</v>
@@ -5619,10 +5568,10 @@
         <v>10</v>
       </c>
       <c r="Q5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -5637,13 +5586,13 @@
         <v>3</v>
       </c>
       <c r="W5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X5">
         <v>3</v>
       </c>
       <c r="Y5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5651,7 +5600,7 @@
         <v>1648</v>
       </c>
       <c r="B6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="5">
         <v>44601.211805555555</v>
@@ -5660,19 +5609,19 @@
         <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H6" t="s">
         <v>83</v>
       </c>
-      <c r="H6" t="s">
-        <v>84</v>
-      </c>
       <c r="I6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J6">
         <v>610</v>
@@ -5687,7 +5636,7 @@
         <v>2</v>
       </c>
       <c r="N6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O6">
         <v>150</v>
@@ -5696,10 +5645,10 @@
         <v>20</v>
       </c>
       <c r="Q6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S6">
         <v>100</v>
@@ -5708,7 +5657,7 @@
         <v>4</v>
       </c>
       <c r="Y6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5716,7 +5665,7 @@
         <v>2891</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="5">
         <v>44605.447916666664</v>
@@ -5725,19 +5674,19 @@
         <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H7" t="s">
+        <v>98</v>
+      </c>
+      <c r="I7" t="s">
         <v>99</v>
-      </c>
-      <c r="I7" t="s">
-        <v>100</v>
       </c>
       <c r="J7">
         <v>1176</v>
@@ -5752,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O7">
         <v>450</v>
@@ -5761,10 +5710,10 @@
         <v>80</v>
       </c>
       <c r="Q7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S7">
         <v>97</v>
@@ -5773,7 +5722,7 @@
         <v>5</v>
       </c>
       <c r="Y7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5781,7 +5730,7 @@
         <v>6796</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="5">
         <v>44618.053472222222</v>
@@ -5790,19 +5739,19 @@
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8" t="s">
         <v>76</v>
       </c>
-      <c r="H8" t="s">
-        <v>77</v>
-      </c>
       <c r="I8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J8">
         <v>215</v>
@@ -5817,7 +5766,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O8">
         <v>60</v>
@@ -5826,10 +5775,10 @@
         <v>80</v>
       </c>
       <c r="Q8" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" t="s">
         <v>79</v>
-      </c>
-      <c r="R8" t="s">
-        <v>80</v>
       </c>
       <c r="S8">
         <v>18</v>
@@ -5838,7 +5787,7 @@
         <v>6</v>
       </c>
       <c r="Y8" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5846,7 +5795,7 @@
         <v>4297</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="5">
         <v>44609.390972222223</v>
@@ -5855,19 +5804,19 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9">
         <v>3838</v>
@@ -5882,7 +5831,7 @@
         <v>3</v>
       </c>
       <c r="N9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O9">
         <v>120</v>
@@ -5891,10 +5840,10 @@
         <v>35</v>
       </c>
       <c r="Q9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -5906,7 +5855,7 @@
         <v>7</v>
       </c>
       <c r="Y9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5914,7 +5863,7 @@
         <v>1556</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C10" s="5">
         <v>44601.120833333334</v>
@@ -5923,19 +5872,19 @@
         <v>18</v>
       </c>
       <c r="E10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" t="s">
         <v>83</v>
       </c>
-      <c r="H10" t="s">
-        <v>84</v>
-      </c>
       <c r="I10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J10">
         <v>3455</v>
@@ -5950,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O10">
         <v>35</v>
@@ -5959,10 +5908,10 @@
         <v>0</v>
       </c>
       <c r="Q10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S10">
         <v>88</v>
@@ -5971,7 +5920,7 @@
         <v>8</v>
       </c>
       <c r="Y10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5979,7 +5928,7 @@
         <v>5922</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C11" s="5">
         <v>44617.210416666669</v>
@@ -5988,19 +5937,19 @@
         <v>25</v>
       </c>
       <c r="E11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F11" t="s">
         <v>74</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>75</v>
       </c>
-      <c r="G11" t="s">
+      <c r="H11" t="s">
         <v>76</v>
       </c>
-      <c r="H11" t="s">
-        <v>77</v>
-      </c>
       <c r="I11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="J11">
         <v>731</v>
@@ -6015,7 +5964,7 @@
         <v>0</v>
       </c>
       <c r="N11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O11">
         <v>140</v>
@@ -6024,10 +5973,10 @@
         <v>10</v>
       </c>
       <c r="Q11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R11" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S11">
         <v>50</v>
@@ -6042,7 +5991,7 @@
         <v>9</v>
       </c>
       <c r="Y11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6050,7 +5999,7 @@
         <v>1694</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C12" s="5">
         <v>44601.181944444441</v>
@@ -6059,19 +6008,19 @@
         <v>30</v>
       </c>
       <c r="E12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" t="s">
         <v>83</v>
       </c>
-      <c r="H12" t="s">
-        <v>84</v>
-      </c>
       <c r="I12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J12">
         <v>3538</v>
@@ -6086,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O12">
         <v>200</v>
@@ -6095,10 +6044,10 @@
         <v>25</v>
       </c>
       <c r="Q12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -6113,13 +6062,13 @@
         <v>16</v>
       </c>
       <c r="W12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6127,7 +6076,7 @@
         <v>1707</v>
       </c>
       <c r="B13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C13" s="5">
         <v>44601.337500000001</v>
@@ -6136,19 +6085,19 @@
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
+        <v>82</v>
+      </c>
+      <c r="H13" t="s">
         <v>83</v>
       </c>
-      <c r="H13" t="s">
-        <v>84</v>
-      </c>
       <c r="I13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J13">
         <v>318</v>
@@ -6163,7 +6112,7 @@
         <v>0</v>
       </c>
       <c r="N13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O13">
         <v>200</v>
@@ -6172,10 +6121,10 @@
         <v>10</v>
       </c>
       <c r="Q13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -6184,7 +6133,7 @@
         <v>11</v>
       </c>
       <c r="Y13" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6192,7 +6141,7 @@
         <v>4009</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="5">
         <v>44608.175694444442</v>
@@ -6201,19 +6150,19 @@
         <v>35</v>
       </c>
       <c r="E14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G14" t="s">
+        <v>82</v>
+      </c>
+      <c r="H14" t="s">
         <v>90</v>
       </c>
-      <c r="G14" t="s">
-        <v>83</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
-      </c>
       <c r="I14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J14">
         <v>128</v>
@@ -6228,7 +6177,7 @@
         <v>3</v>
       </c>
       <c r="N14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O14">
         <v>210</v>
@@ -6237,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="Q14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -6249,7 +6198,7 @@
         <v>12</v>
       </c>
       <c r="Y14" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6257,7 +6206,7 @@
         <v>6443</v>
       </c>
       <c r="B15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C15" s="5">
         <v>44618.205555555556</v>
@@ -6266,19 +6215,19 @@
         <v>18</v>
       </c>
       <c r="E15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
         <v>75</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>76</v>
       </c>
-      <c r="H15" t="s">
-        <v>77</v>
-      </c>
       <c r="I15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J15">
         <v>2510</v>
@@ -6293,7 +6242,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>60</v>
@@ -6302,10 +6251,10 @@
         <v>10</v>
       </c>
       <c r="Q15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S15">
         <v>62</v>
@@ -6320,13 +6269,13 @@
         <v>23</v>
       </c>
       <c r="W15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X15">
         <v>13</v>
       </c>
       <c r="Y15" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6334,7 +6283,7 @@
         <v>5680</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C16" s="5">
         <v>44615.270833333336</v>
@@ -6343,19 +6292,19 @@
         <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G16" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J16">
         <v>633</v>
@@ -6370,7 +6319,7 @@
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O16">
         <v>280</v>
@@ -6379,10 +6328,10 @@
         <v>70</v>
       </c>
       <c r="Q16" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S16">
         <v>30</v>
@@ -6397,13 +6346,13 @@
         <v>10</v>
       </c>
       <c r="W16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X16">
         <v>14</v>
       </c>
       <c r="Y16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6411,7 +6360,7 @@
         <v>4924</v>
       </c>
       <c r="B17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C17" s="5">
         <v>44613.43472222222</v>
@@ -6420,19 +6369,19 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J17">
         <v>706</v>
@@ -6447,7 +6396,7 @@
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>35</v>
@@ -6456,10 +6405,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S17">
         <v>70</v>
@@ -6468,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="Y17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6476,7 +6425,7 @@
         <v>3288</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="5">
         <v>44606.345138888886</v>
@@ -6485,19 +6434,19 @@
         <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H18" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J18">
         <v>1581</v>
@@ -6512,7 +6461,7 @@
         <v>2</v>
       </c>
       <c r="N18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O18">
         <v>200</v>
@@ -6521,10 +6470,10 @@
         <v>40</v>
       </c>
       <c r="Q18" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S18">
         <v>82</v>
@@ -6539,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="W18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X18">
         <v>16</v>
       </c>
       <c r="Y18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6553,7 +6502,7 @@
         <v>3940</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="5">
         <v>44608.157638888886</v>
@@ -6562,19 +6511,19 @@
         <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" t="s">
         <v>90</v>
       </c>
-      <c r="G19" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" t="s">
-        <v>91</v>
-      </c>
       <c r="I19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J19">
         <v>1454</v>
@@ -6589,7 +6538,7 @@
         <v>0</v>
       </c>
       <c r="N19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O19">
         <v>100</v>
@@ -6598,10 +6547,10 @@
         <v>20</v>
       </c>
       <c r="Q19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S19">
         <v>72</v>
@@ -6610,7 +6559,7 @@
         <v>17</v>
       </c>
       <c r="Y19" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6618,7 +6567,7 @@
         <v>3140</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C20" s="5">
         <v>44605.251388888886</v>
@@ -6627,19 +6576,19 @@
         <v>41</v>
       </c>
       <c r="E20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" t="s">
         <v>74</v>
       </c>
-      <c r="F20" t="s">
-        <v>75</v>
-      </c>
       <c r="G20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20">
         <v>1498</v>
@@ -6654,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="N20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O20">
         <v>50</v>
@@ -6663,10 +6612,10 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S20">
         <v>50</v>
@@ -6675,7 +6624,7 @@
         <v>18</v>
       </c>
       <c r="Y20" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6683,7 +6632,7 @@
         <v>4106</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C21" s="5">
         <v>44608.160416666666</v>
@@ -6692,19 +6641,19 @@
         <v>31</v>
       </c>
       <c r="E21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" t="s">
         <v>74</v>
       </c>
-      <c r="F21" t="s">
-        <v>75</v>
-      </c>
       <c r="G21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I21" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J21">
         <v>834</v>
@@ -6719,7 +6668,7 @@
         <v>3</v>
       </c>
       <c r="N21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O21">
         <v>350</v>
@@ -6728,10 +6677,10 @@
         <v>50</v>
       </c>
       <c r="Q21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R21" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S21">
         <v>34</v>
@@ -6746,13 +6695,13 @@
         <v>3</v>
       </c>
       <c r="W21" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X21">
         <v>19</v>
       </c>
       <c r="Y21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6760,7 +6709,7 @@
         <v>1458</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C22" s="5">
         <v>44600.42083333333</v>
@@ -6769,19 +6718,19 @@
         <v>50</v>
       </c>
       <c r="E22" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F22" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
+        <v>82</v>
+      </c>
+      <c r="H22" t="s">
         <v>83</v>
       </c>
-      <c r="H22" t="s">
-        <v>84</v>
-      </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J22">
         <v>2006</v>
@@ -6796,7 +6745,7 @@
         <v>1</v>
       </c>
       <c r="N22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O22">
         <v>300</v>
@@ -6805,10 +6754,10 @@
         <v>7000</v>
       </c>
       <c r="Q22" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R22" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -6823,13 +6772,13 @@
         <v>3</v>
       </c>
       <c r="W22" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X22">
         <v>20</v>
       </c>
       <c r="Y22" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6837,7 +6786,7 @@
         <v>2149</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="5">
         <v>44602.234027777777</v>
@@ -6846,19 +6795,19 @@
         <v>69</v>
       </c>
       <c r="E23" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s">
+        <v>82</v>
+      </c>
+      <c r="H23" t="s">
         <v>83</v>
       </c>
-      <c r="H23" t="s">
-        <v>84</v>
-      </c>
       <c r="I23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J23">
         <v>3510</v>
@@ -6873,7 +6822,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -6882,10 +6831,10 @@
         <v>15</v>
       </c>
       <c r="Q23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -6897,13 +6846,13 @@
         <v>10</v>
       </c>
       <c r="W23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X23">
         <v>21</v>
       </c>
       <c r="Y23" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6911,7 +6860,7 @@
         <v>415</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="5">
         <v>44597.34652777778</v>
@@ -6920,19 +6869,19 @@
         <v>50</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F24" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I24" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J24">
         <v>1736</v>
@@ -6947,7 +6896,7 @@
         <v>4</v>
       </c>
       <c r="N24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O24">
         <v>170</v>
@@ -6956,10 +6905,10 @@
         <v>50</v>
       </c>
       <c r="Q24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R24" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S24">
         <v>11</v>
@@ -6968,7 +6917,7 @@
         <v>22</v>
       </c>
       <c r="Y24" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -6976,7 +6925,7 @@
         <v>4785</v>
       </c>
       <c r="B25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="5">
         <v>44613.245138888888</v>
@@ -6985,19 +6934,19 @@
         <v>30</v>
       </c>
       <c r="E25" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F25" t="s">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s">
         <v>75</v>
       </c>
-      <c r="G25" t="s">
-        <v>76</v>
-      </c>
       <c r="H25" t="s">
+        <v>112</v>
+      </c>
+      <c r="I25" t="s">
         <v>113</v>
-      </c>
-      <c r="I25" t="s">
-        <v>114</v>
       </c>
       <c r="J25">
         <v>175</v>
@@ -7012,7 +6961,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O25">
         <v>150</v>
@@ -7021,10 +6970,10 @@
         <v>50</v>
       </c>
       <c r="Q25" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R25" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -7033,7 +6982,7 @@
         <v>23</v>
       </c>
       <c r="Y25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7041,7 +6990,7 @@
         <v>4134</v>
       </c>
       <c r="B26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C26" s="5">
         <v>44609.234027777777</v>
@@ -7050,19 +6999,19 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" t="s">
         <v>74</v>
       </c>
-      <c r="F26" t="s">
-        <v>75</v>
-      </c>
       <c r="G26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J26">
         <v>695</v>
@@ -7077,7 +7026,7 @@
         <v>0</v>
       </c>
       <c r="N26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O26">
         <v>210</v>
@@ -7086,10 +7035,10 @@
         <v>15</v>
       </c>
       <c r="Q26" t="s">
+        <v>78</v>
+      </c>
+      <c r="R26" t="s">
         <v>79</v>
-      </c>
-      <c r="R26" t="s">
-        <v>80</v>
       </c>
       <c r="S26">
         <v>65</v>
@@ -7098,7 +7047,7 @@
         <v>24</v>
       </c>
       <c r="Y26" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7106,7 +7055,7 @@
         <v>6489</v>
       </c>
       <c r="B27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C27" s="5">
         <v>44618.247916666667</v>
@@ -7115,19 +7064,19 @@
         <v>46</v>
       </c>
       <c r="E27" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G27" t="s">
+        <v>75</v>
+      </c>
+      <c r="H27" t="s">
         <v>76</v>
       </c>
-      <c r="H27" t="s">
-        <v>77</v>
-      </c>
       <c r="I27" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J27">
         <v>407</v>
@@ -7142,7 +7091,7 @@
         <v>2</v>
       </c>
       <c r="N27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O27">
         <v>210</v>
@@ -7151,10 +7100,10 @@
         <v>70</v>
       </c>
       <c r="Q27" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S27">
         <v>5</v>
@@ -7163,7 +7112,7 @@
         <v>25</v>
       </c>
       <c r="Y27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7171,7 +7120,7 @@
         <v>1526</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C28" s="5">
         <v>44600.460416666669</v>
@@ -7180,19 +7129,19 @@
         <v>22</v>
       </c>
       <c r="E28" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G28" t="s">
+        <v>82</v>
+      </c>
+      <c r="H28" t="s">
         <v>83</v>
       </c>
-      <c r="H28" t="s">
-        <v>84</v>
-      </c>
       <c r="I28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J28">
         <v>4422</v>
@@ -7207,7 +7156,7 @@
         <v>1</v>
       </c>
       <c r="N28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O28">
         <v>210</v>
@@ -7216,10 +7165,10 @@
         <v>40</v>
       </c>
       <c r="Q28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R28" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S28">
         <v>83</v>
@@ -7228,7 +7177,7 @@
         <v>26</v>
       </c>
       <c r="Y28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7236,7 +7185,7 @@
         <v>3093</v>
       </c>
       <c r="B29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C29" s="5">
         <v>44605.17083333333</v>
@@ -7245,19 +7194,19 @@
         <v>31</v>
       </c>
       <c r="E29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J29">
         <v>1066</v>
@@ -7272,7 +7221,7 @@
         <v>3</v>
       </c>
       <c r="N29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O29">
         <v>180</v>
@@ -7281,10 +7230,10 @@
         <v>140</v>
       </c>
       <c r="Q29" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R29" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S29">
         <v>20</v>
@@ -7299,13 +7248,13 @@
         <v>0</v>
       </c>
       <c r="W29" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X29">
         <v>27</v>
       </c>
       <c r="Y29" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7313,7 +7262,7 @@
         <v>4975</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C30" s="5">
         <v>44613.315972222219</v>
@@ -7322,19 +7271,19 @@
         <v>26</v>
       </c>
       <c r="E30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" t="s">
         <v>112</v>
       </c>
-      <c r="G30" t="s">
-        <v>76</v>
-      </c>
-      <c r="H30" t="s">
-        <v>113</v>
-      </c>
       <c r="I30" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J30">
         <v>167</v>
@@ -7349,7 +7298,7 @@
         <v>0</v>
       </c>
       <c r="N30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O30">
         <v>400</v>
@@ -7358,10 +7307,10 @@
         <v>30</v>
       </c>
       <c r="Q30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S30">
         <v>10</v>
@@ -7370,7 +7319,7 @@
         <v>28</v>
       </c>
       <c r="Y30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7378,7 +7327,7 @@
         <v>2191</v>
       </c>
       <c r="B31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C31" s="5">
         <v>44602.135416666664</v>
@@ -7387,19 +7336,19 @@
         <v>26</v>
       </c>
       <c r="E31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F31" t="s">
+        <v>135</v>
+      </c>
+      <c r="G31" t="s">
+        <v>82</v>
+      </c>
+      <c r="H31" t="s">
+        <v>83</v>
+      </c>
+      <c r="I31" t="s">
         <v>136</v>
-      </c>
-      <c r="G31" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" t="s">
-        <v>137</v>
       </c>
       <c r="J31">
         <v>1580</v>
@@ -7414,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="N31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O31">
         <v>200</v>
@@ -7423,10 +7372,10 @@
         <v>20</v>
       </c>
       <c r="Q31" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="R31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S31">
         <v>31</v>
@@ -7441,13 +7390,13 @@
         <v>100</v>
       </c>
       <c r="W31" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X31">
         <v>29</v>
       </c>
       <c r="Y31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7455,7 +7404,7 @@
         <v>538</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C32" s="5">
         <v>44597.540972222225</v>
@@ -7464,19 +7413,19 @@
         <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F32" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J32">
         <v>1201</v>
@@ -7491,7 +7440,7 @@
         <v>3</v>
       </c>
       <c r="N32" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O32">
         <v>150</v>
@@ -7500,10 +7449,10 @@
         <v>15</v>
       </c>
       <c r="Q32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S32">
         <v>100</v>
@@ -7512,7 +7461,7 @@
         <v>30</v>
       </c>
       <c r="Y32" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="33" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7520,7 +7469,7 @@
         <v>3679</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C33" s="5">
         <v>44606.201388888891</v>
@@ -7529,19 +7478,19 @@
         <v>57</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" t="s">
         <v>82</v>
       </c>
-      <c r="G33" t="s">
-        <v>83</v>
-      </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I33" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J33">
         <v>1040</v>
@@ -7556,7 +7505,7 @@
         <v>5</v>
       </c>
       <c r="N33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O33">
         <v>350</v>
@@ -7565,10 +7514,10 @@
         <v>180</v>
       </c>
       <c r="Q33" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="R33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S33">
         <v>51</v>
@@ -7583,13 +7532,13 @@
         <v>42</v>
       </c>
       <c r="W33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X33">
         <v>31</v>
       </c>
       <c r="Y33" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="34" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7597,7 +7546,7 @@
         <v>4806</v>
       </c>
       <c r="B34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="5">
         <v>44613.434027777781</v>
@@ -7606,19 +7555,19 @@
         <v>43</v>
       </c>
       <c r="E34" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F34" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I34" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J34">
         <v>1398</v>
@@ -7633,7 +7582,7 @@
         <v>4</v>
       </c>
       <c r="N34" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O34">
         <v>200</v>
@@ -7642,10 +7591,10 @@
         <v>20</v>
       </c>
       <c r="Q34" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R34" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S34">
         <v>71</v>
@@ -7654,7 +7603,7 @@
         <v>32</v>
       </c>
       <c r="Y34" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7662,7 +7611,7 @@
         <v>4604</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="5">
         <v>44610.093055555553</v>
@@ -7671,19 +7620,19 @@
         <v>68</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I35" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J35">
         <v>417</v>
@@ -7698,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O35">
         <v>100</v>
@@ -7707,10 +7656,10 @@
         <v>30</v>
       </c>
       <c r="Q35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S35">
         <v>80</v>
@@ -7719,7 +7668,7 @@
         <v>33</v>
       </c>
       <c r="Y35" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="36" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7727,7 +7676,7 @@
         <v>4085</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C36" s="5">
         <v>44609.120138888888</v>
@@ -7736,19 +7685,19 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F36" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I36" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J36">
         <v>855</v>
@@ -7763,7 +7712,7 @@
         <v>0</v>
       </c>
       <c r="N36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O36">
         <v>240</v>
@@ -7772,10 +7721,10 @@
         <v>100</v>
       </c>
       <c r="Q36" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -7784,7 +7733,7 @@
         <v>34</v>
       </c>
       <c r="Y36" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="37" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7792,7 +7741,7 @@
         <v>2141</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C37" s="5">
         <v>44602.143750000003</v>
@@ -7801,19 +7750,19 @@
         <v>20</v>
       </c>
       <c r="E37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s">
+        <v>82</v>
+      </c>
+      <c r="H37" t="s">
         <v>83</v>
       </c>
-      <c r="H37" t="s">
-        <v>84</v>
-      </c>
       <c r="I37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J37">
         <v>3510</v>
@@ -7828,7 +7777,7 @@
         <v>1</v>
       </c>
       <c r="N37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O37">
         <v>350</v>
@@ -7837,10 +7786,10 @@
         <v>15</v>
       </c>
       <c r="Q37" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R37" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -7849,7 +7798,7 @@
         <v>35</v>
       </c>
       <c r="Y37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7857,7 +7806,7 @@
         <v>3794</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" s="5">
         <v>44608.310416666667</v>
@@ -7866,19 +7815,19 @@
         <v>18</v>
       </c>
       <c r="E38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H38" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J38">
         <v>1465</v>
@@ -7893,7 +7842,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="O38">
         <v>140</v>
@@ -7902,10 +7851,10 @@
         <v>80</v>
       </c>
       <c r="Q38" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R38" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S38">
         <v>92</v>
@@ -7914,7 +7863,7 @@
         <v>36</v>
       </c>
       <c r="Y38" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="39" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7922,7 +7871,7 @@
         <v>3355</v>
       </c>
       <c r="B39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" s="5">
         <v>44606.291666666664</v>
@@ -7931,19 +7880,19 @@
         <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J39">
         <v>629</v>
@@ -7958,7 +7907,7 @@
         <v>1</v>
       </c>
       <c r="N39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O39">
         <v>55</v>
@@ -7967,10 +7916,10 @@
         <v>0</v>
       </c>
       <c r="Q39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S39">
         <v>91</v>
@@ -7979,7 +7928,7 @@
         <v>37</v>
       </c>
       <c r="Y39" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -7987,7 +7936,7 @@
         <v>1736</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C40" s="5">
         <v>44601.129166666666</v>
@@ -7996,19 +7945,19 @@
         <v>58</v>
       </c>
       <c r="E40" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s">
+        <v>82</v>
+      </c>
+      <c r="H40" t="s">
         <v>83</v>
       </c>
-      <c r="H40" t="s">
-        <v>84</v>
-      </c>
       <c r="I40" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J40">
         <v>714</v>
@@ -8023,7 +7972,7 @@
         <v>4</v>
       </c>
       <c r="N40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O40">
         <v>100</v>
@@ -8032,10 +7981,10 @@
         <v>45</v>
       </c>
       <c r="Q40" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S40">
         <v>90</v>
@@ -8050,13 +7999,13 @@
         <v>2</v>
       </c>
       <c r="W40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X40">
         <v>38</v>
       </c>
       <c r="Y40" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8064,7 +8013,7 @@
         <v>5144</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C41" s="5">
         <v>44614.393750000003</v>
@@ -8073,19 +8022,19 @@
         <v>24</v>
       </c>
       <c r="E41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H41" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J41">
         <v>235</v>
@@ -8100,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O41">
         <v>210</v>
@@ -8109,10 +8058,10 @@
         <v>50</v>
       </c>
       <c r="Q41" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R41" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -8127,13 +8076,13 @@
         <v>10</v>
       </c>
       <c r="W41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="X41">
         <v>39</v>
       </c>
       <c r="Y41" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8141,7 +8090,7 @@
         <v>4497</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C42" s="5">
         <v>44609.114583333336</v>
@@ -8150,19 +8099,19 @@
         <v>22</v>
       </c>
       <c r="E42" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G42" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I42" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J42">
         <v>984</v>
@@ -8177,7 +8126,7 @@
         <v>3</v>
       </c>
       <c r="N42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O42">
         <v>300</v>
@@ -8186,10 +8135,10 @@
         <v>10</v>
       </c>
       <c r="Q42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S42">
         <v>91</v>
@@ -8198,7 +8147,7 @@
         <v>40</v>
       </c>
       <c r="Y42" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8206,7 +8155,7 @@
         <v>3483</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C43" s="5">
         <v>44606.379861111112</v>
@@ -8215,19 +8164,19 @@
         <v>30</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F43" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H43" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I43" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="J43">
         <v>296</v>
@@ -8242,7 +8191,7 @@
         <v>1</v>
       </c>
       <c r="N43" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O43">
         <v>35</v>
@@ -8251,10 +8200,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="R43" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S43">
         <v>76</v>
@@ -8263,7 +8212,7 @@
         <v>41</v>
       </c>
       <c r="Y43" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8271,7 +8220,7 @@
         <v>6450</v>
       </c>
       <c r="B44" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C44" s="5">
         <v>44618.227083333331</v>
@@ -8280,19 +8229,19 @@
         <v>24</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F44" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s">
+        <v>75</v>
+      </c>
+      <c r="H44" t="s">
         <v>76</v>
       </c>
-      <c r="H44" t="s">
-        <v>77</v>
-      </c>
       <c r="I44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J44">
         <v>407</v>
@@ -8307,7 +8256,7 @@
         <v>4</v>
       </c>
       <c r="N44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O44">
         <v>100</v>
@@ -8316,10 +8265,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R44" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S44">
         <v>61</v>
@@ -8328,7 +8277,7 @@
         <v>42</v>
       </c>
       <c r="Y44" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8336,7 +8285,7 @@
         <v>2882</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="5">
         <v>44605.368750000001</v>
@@ -8345,19 +8294,19 @@
         <v>24</v>
       </c>
       <c r="E45" t="s">
+        <v>73</v>
+      </c>
+      <c r="F45" t="s">
         <v>74</v>
       </c>
-      <c r="F45" t="s">
-        <v>75</v>
-      </c>
       <c r="G45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H45" t="s">
+        <v>98</v>
+      </c>
+      <c r="I45" t="s">
         <v>99</v>
-      </c>
-      <c r="I45" t="s">
-        <v>100</v>
       </c>
       <c r="J45">
         <v>1176</v>
@@ -8372,7 +8321,7 @@
         <v>1</v>
       </c>
       <c r="N45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O45">
         <v>320</v>
@@ -8381,10 +8330,10 @@
         <v>40</v>
       </c>
       <c r="Q45" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R45" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S45">
         <v>97</v>
@@ -8399,13 +8348,13 @@
         <v>10</v>
       </c>
       <c r="W45" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="X45">
         <v>43</v>
       </c>
       <c r="Y45" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8413,7 +8362,7 @@
         <v>4757</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" s="5">
         <v>44610.291666666664</v>
@@ -8422,19 +8371,19 @@
         <v>24</v>
       </c>
       <c r="E46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G46" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I46" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="J46">
         <v>4620</v>
@@ -8449,7 +8398,7 @@
         <v>5</v>
       </c>
       <c r="N46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="O46">
         <v>300</v>
@@ -8458,10 +8407,10 @@
         <v>100</v>
       </c>
       <c r="Q46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S46">
         <v>70</v>
@@ -8476,13 +8425,13 @@
         <v>26</v>
       </c>
       <c r="W46" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="X46">
         <v>44</v>
       </c>
       <c r="Y46" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="47" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -8490,7 +8439,7 @@
         <v>1929</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" s="5">
         <v>44601.813194444447</v>
@@ -8499,19 +8448,19 @@
         <v>26</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F47" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G47" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" t="s">
         <v>83</v>
       </c>
-      <c r="H47" t="s">
-        <v>84</v>
-      </c>
       <c r="I47" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J47">
         <v>4995</v>
@@ -8526,7 +8475,7 @@
         <v>3</v>
       </c>
       <c r="N47" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O47">
         <v>150</v>
@@ -8535,10 +8484,10 @@
         <v>30</v>
       </c>
       <c r="Q47" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="R47" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S47">
         <v>49</v>
@@ -8547,7 +8496,7 @@
         <v>45</v>
       </c>
       <c r="Y47" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -24367,7 +24316,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
@@ -24375,10 +24324,10 @@
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/demos/rct_experiment/rct_experiment_prompt_template.xlsx
+++ b/demos/rct_experiment/rct_experiment_prompt_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/raymondlow/Documents/talking-to-machines/talking-to-machines/demos/rct_experiment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A27529-10BF-B94E-A103-0BA731517645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34142A34-D20B-3347-BF3E-48EEAA1665CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="3760" windowWidth="34560" windowHeight="20140" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1840" yWindow="-21100" windowWidth="26920" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="settings" sheetId="1" r:id="rId1"/>
@@ -537,11 +537,6 @@
   </si>
   <si>
     <t>{
-"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID 19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. Getting the COVID-19 vaccine will help prevent you from getting COVID-19 and reduce your risk of being hospitalized with COVID-19. COVID 19 vaccine help you to protect yourself your environment and your loved ones from COVID-19 exposure.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification"
-}</t>
-  </si>
-  <si>
-    <t>{
 "description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nThe Sun lights up our lives for business for education even for socializing but when the Sun sets many people use candles who are quality battery-operated torches and kerosene lamps as inefficient and expensive ways to create light. What if you can take some Sun with you at night?  You can with portable solar products there are different types, but each portable solar product is made up of three basic parts: a small solar panel, a modern rechargeable battery and an LED bulb. The solar panel catches the light from the Sun and stores this energy in the battery. This can now be used for much needed light when it's dark. Many can even charge phones portable solar products should be reliable affordable and warranted be sure to demand top quality solar products look for these products lighting Africa shining the way.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status.  If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification."
 }</t>
   </si>
@@ -603,6 +598,11 @@
   </si>
   <si>
     <t>session_id</t>
+  </si>
+  <si>
+    <t>{
+"description":"You are asked to watch a video at this point. Here you are provided with the transcript of the video.\nHealth authorities are working hard to distribute the COVID-19 vaccines free for everyone with no strings attached. COVID 19 vaccines are safe and effective. After you have been fully vaccinated you can resume activities that you did prior to the pandemic. Getting the COVID-19 vaccine will help prevent you from getting COVID-19 and reduce your risk of being hospitalized with COVID-19. COVID 19 vaccine help you to protect yourself your environment and your loved ones from COVID-19 exposure.\n\nWe indicated that we will follow up with you in 6 weeks. We will contact you in order to verify your vaccination status. If you can provide us with your COVID-19 vaccination carnet at the time, we will upload a copy of the vaccination carnet to our secure server for verification."
+}</t>
   </si>
 </sst>
 </file>
@@ -901,7 +901,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>156</v>
@@ -920,7 +920,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -955,10 +955,10 @@
     </row>
     <row r="8" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B8" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -1030,7 +1030,7 @@
         <v>165</v>
       </c>
       <c r="B17" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2072,7 +2072,7 @@
         <v>85</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2080,7 +2080,7 @@
         <v>72</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2088,7 +2088,7 @@
         <v>102</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2096,7 +2096,7 @@
         <v>80</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3122,10 +3122,10 @@
     </row>
     <row r="2" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -3133,7 +3133,7 @@
         <v>155</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4137,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M847"/>
+  <dimension ref="A1:M843"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="3" customWidth="1"/>
@@ -4159,13 +4159,13 @@
   <sheetData>
     <row r="1" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>9</v>
@@ -4177,10 +4177,10 @@
         <v>11</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>12</v>
@@ -4251,13 +4251,13 @@
         <v>0</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>181</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>182</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>16</v>
@@ -4293,7 +4293,7 @@
         <v>70</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>150</v>
@@ -4334,7 +4334,7 @@
         <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>151</v>
@@ -4359,9 +4359,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E7" s="7"/>
-    </row>
+    <row r="7" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="8" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="9" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5198,17 +5196,10 @@
     <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H4 H6:H1048576" xr:uid="{B52963B2-1D08-9B4B-A4B6-B266870FC6FB}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H2:H1048576" xr:uid="{B52963B2-1D08-9B4B-A4B6-B266870FC6FB}">
       <formula1>"context, category, integer, free-text"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="H5" xr:uid="{2FDB2F7E-ECDB-E740-A5BE-8D2E81EF5F27}">
-      <formula1>"context, category, integer"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Value" error="Please choose an option from the dropdown list." sqref="J2:M1048576 D2:D1048576" xr:uid="{4BB7CE7C-18FC-BB40-9E15-025F5FDB5F2D}">
       <formula1>"True, False"</formula1>
